--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00940-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00940-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{405ED54C-9040-4CAB-A690-0217D5DC79E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEC5930C-695F-433E-96D3-7CB68573E49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{585D78BD-79AE-4FC6-AE9F-997D08E7FCEE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{97CA40D6-D1B5-42C6-B414-929580045DDD}"/>
   </bookViews>
   <sheets>
     <sheet name="00940-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1594,24 +1594,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F40C4D-F036-4898-BE78-9A2AAC653E3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5706814E-16D6-4947-9C66-F439593091E0}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1640,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1669,7 +1670,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1765,7 +1766,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1845,7 +1846,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1901,7 +1902,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -2013,7 +2014,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>2025</v>
       </c>
@@ -2067,7 +2068,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2179,7 +2180,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2235,7 +2236,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2291,7 +2292,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2347,7 +2348,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2403,7 +2404,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2459,7 +2460,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2627,7 +2628,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>26</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2024</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2849,7 +2850,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2905,7 +2906,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2961,7 +2962,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3017,7 +3018,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3073,7 +3074,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3129,7 +3130,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="49" t="s">
         <v>69</v>
       </c>
